--- a/Result/profitability/2364.xlsx
+++ b/Result/profitability/2364.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>0.91125</v>
+        <v>1.00625</v>
       </c>
       <c r="N2" t="n">
-        <v>35.695</v>
+        <v>36.08875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7075</v>
+        <v>0.88625</v>
       </c>
       <c r="N3" t="n">
-        <v>32.03375</v>
+        <v>33.1025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.7087500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>28.90375</v>
+        <v>29.7225</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4525</v>
+        <v>0.6950000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>25.90375</v>
+        <v>26.34875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.40375</v>
+        <v>0.455</v>
       </c>
       <c r="N6" t="n">
-        <v>22.64375</v>
+        <v>22.8625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.14125</v>
+        <v>0.28625</v>
       </c>
       <c r="N7" t="n">
-        <v>18.7425</v>
+        <v>19.22125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.39</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.13375</v>
       </c>
       <c r="N8" t="n">
-        <v>14.4875</v>
+        <v>15.1425</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2364</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>519</v>
+      </c>
+      <c r="D75" t="n">
+        <v>292</v>
+      </c>
+      <c r="E75" t="n">
+        <v>227</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>111</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>117</v>
+      </c>
+      <c r="K75" t="n">
+        <v>116</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.2375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.62125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.674698795180723</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.240000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1362454498179928</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>6.928571428571429</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.560000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08868958644743397</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
